--- a/光伏配储项目/电价数据/2026/南屏站.xlsx
+++ b/光伏配储项目/电价数据/2026/南屏站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55357</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.51137</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8520399999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12333</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01327</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.9084800000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.70588</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7155900000000001</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5330499999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.5851900000000001</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.5186499999999999</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.67698</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.67711</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.66728</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51193</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.69502</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.6851799999999999</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.64761</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.67347</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.6880299999999999</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.54074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.6860700000000001</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.6939500000000001</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.5448999999999999</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.7189800000000001</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.80859</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85639</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6708099999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73239</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7550800000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.00764</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.99183</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.0827</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.74981</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.6964600000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50069</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.78299</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.94772</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31023</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52258</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7583099999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76619</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74634</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9261200000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.8928200000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04618</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31289</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.11829</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.11472</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.73323</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.20761</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16735</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09616</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22702</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53385</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.09941</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24521</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.4748</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23462</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79736</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.40881</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35251</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28309</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.80248</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16667</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03651</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17606</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51237</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.60861</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.50873</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.58292</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.48756</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48098</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.49726</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.49726</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.50414</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.55271</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.75961</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.0627</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83433</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.58625</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.47994</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45318</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.50505</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.93344</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.14934</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.77444</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11905</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03622</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.98473</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.70662</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5474199999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56614</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.67849</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15112</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.22898</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47268</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15598</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.62676</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07761</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8163899999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.24948</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13393</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28232</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62137</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56975</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6215900000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16632</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17504</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.16967</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9663999999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.1878</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.2026</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19397</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66846</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.15936</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20544</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.2074</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50361</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.40809</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16568</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50963</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26384</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74236</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76488</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5991000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6776799999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.68851</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.52973</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.5730499999999999</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5041</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.82092</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.58727</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.57929</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.54831</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55198</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6263</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48038</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.57472</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48383</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.57102</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.5205299999999999</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.55203</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.48948</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.50695</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.49181</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50212</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83017</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10719</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.8732799999999999</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.74349</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.7024600000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60411</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6429900000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72815</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16311</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.51947</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6758200000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16525</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.61808</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.1872</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16307</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7918200000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.93755</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16179</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.16329</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.89123</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.55925</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47449</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67389</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16408</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02694</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16243</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.38996</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23304</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16383</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21521</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20913</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.39856</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26738</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28443</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64718</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.16884</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17188</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78009</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03719</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07689</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09775</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08382</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20246</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16655</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24631</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.99322</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75334</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.70985</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.52967</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10657</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.71609</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.70966</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.17008</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6746599999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.84896</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.53562</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.56916</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.18618</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.58535</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.5182</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.6466000000000001</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.57745</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5179900000000001</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.51117</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.50454</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44112</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.50304</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.51613</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.56938</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.4889</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.48948</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.45485</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48803</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6757000000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7179</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16606</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30725</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8365</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.54963</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66541</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9030199999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8628400000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.1624</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43925</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77219</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9511499999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20229</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.68791</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12261</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52191</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48477</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6532899999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.99433</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10106</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24802</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16659</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.05877</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.97975</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02511</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9890599999999999</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.24909</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.43891</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.7917999999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34655</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.18765</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18863</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.8464700000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07213</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.15931</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12076</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15186</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.25282</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31644</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15191</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26768</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18672</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18567</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18684</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18684</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17235</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.14994</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17512</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72274</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52219</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72488</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74322</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49321</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47726</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50412</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45424</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71566</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.84684</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61412</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70087</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7259</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.84439</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70436</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55011</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54915</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.53789</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59168</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47006</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08431</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.54952</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51145</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46612</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.63218</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48253</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48267</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48686</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.59341</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50543</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48565</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34387</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.18926</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96413</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.58973</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.64312</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.5236000000000001</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.5374800000000001</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.50574</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.50449</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.67375</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.5205700000000001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.5208700000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.50402</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.5047900000000001</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26816</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07327</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04527</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08275</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12855</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04503</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00289</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04678</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25232</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26791</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44574</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.58736</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.53226</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.55464</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.53412</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.53332</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55139</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.26953</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26757</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.74026</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8727200000000001</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.64747</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.74736</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9377300000000001</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48047</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7289500000000001</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7305499999999999</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88635</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.62913</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5350499999999999</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08493000000000001</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73078</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72689</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6377999999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60224</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.72782</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.78852</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7822</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.59975</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.74095</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01728</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40463</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43229</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29471</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.78726</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.37907</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04377</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.79884</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.39934</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76394</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44264</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.77359</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80035</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78501</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5019400000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41134</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46006</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21845</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.6112000000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.57833</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.55813</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.5669299999999999</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.57369</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.57526</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.46419</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.47549</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.5354500000000001</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.50681</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.50717</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.50708</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.54352</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.5080899999999999</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.56109</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.56275</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.48835</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5636100000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66618</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07978</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.63801</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50226</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.56879</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.5988</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00091</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33878</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30636</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27488</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55913</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8018200000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57278</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65052</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5501200000000001</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95439</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7759199999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72505</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6415700000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5748799999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.98702</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.9247000000000001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78427</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.66844</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.58484</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.66687</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.61994</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.6985</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.63727</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.65912</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5815900000000001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5769500000000001</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.6570499999999999</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.6729700000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.6178400000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.66657</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.6853899999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.75985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.75624</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.68528</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.68276</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68445</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.66839</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.6578200000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.61456</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.65695</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.59894</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60194</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.5495099999999999</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5748799999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.53603</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.52547</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57104</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.60011</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.61513</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6732</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.52838</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.5424600000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.49504</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5188700000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.48835</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64037</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51187</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.61693</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.72637</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.86963</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.10916</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9315599999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.54411</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11262</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8421799999999999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.94772</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8577</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.63886</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.80826</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06565</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.5644600000000001</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.5217200000000001</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43186</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.8733300000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.98827</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.52716</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.18794</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.7823300000000001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.81188</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.73468</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.73851</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47496</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49943</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19587</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51229</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79253</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.74779</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16459</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9205800000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64223</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.66084</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.69985</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55355</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16321</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61101</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90844</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57548</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.56708</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.32978</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.25436</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.22216</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.32494</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.00149</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51765</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.60122</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.85819</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50437</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7494299999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.0745</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.0724</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.90438</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93562</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17324</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15237</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.86093</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15372</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60624</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.96893</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01423</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.1531</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.94875</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.98898</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58324</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92257</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08746</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.88397</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.8716</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79206</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09482</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55237</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.95838</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.98933</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74237</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33138</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.60042</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.48738</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.5453600000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.58188</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.49334</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.47432</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.48725</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.48352</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.52638</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83297</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71397</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.5402400000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.56243</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.7137899999999999</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.83869</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.5646100000000001</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.5688300000000001</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.50537</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.50503</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.5521900000000001</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.6102000000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.5520700000000001</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.5645</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.44443</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.45452</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.45688</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.67643</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5380199999999999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.50569</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.50749</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50074</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50431</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56699</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44581</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.56345</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.52175</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.52847</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.5153799999999999</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.4867</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.50908</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.49521</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.52195</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.51776</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.47997</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5538500000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.46989</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48503</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70094</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60278</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62776</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8491299999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27169</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16658</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8523200000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7014900000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94037</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16815</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12183</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01873</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54191</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5630599999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.45705</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.49663</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43339</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.47984</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.50157</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.50273</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.57502</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.7070299999999999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.04413</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.1076</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9905700000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.97929</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9808300000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56612</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54691</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9464400000000001</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08638</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78383</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.0134</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76784</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64841</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64115</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70845</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.8002</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.2987</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.00529</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.59511</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.72792</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.38875</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.21535</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62385</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65749</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67086</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66593</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.6429</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66739</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20689</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70032</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78212</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69763</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70541</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71356</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63313</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74786</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02184</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13165</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69147</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.69991</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69368</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77331</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72347</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81287</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6663300000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46295</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.05911</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.46166</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45189</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34411</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.59485</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17105</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.49434</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.48559</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.50195</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.49483</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.48969</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.74679</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51059</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51883</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45211</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92206</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47446</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17931</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90238</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7633</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45566</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44909</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48984</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.43601</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74639</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42613</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51497</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.67997</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49583</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56623</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45375</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66451</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8316399999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.51861</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48367</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.47875</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.68979</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42504</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5164800000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54612</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76159</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7682899999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.47982</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54673</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5016499999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72333</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76273</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55432</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48752</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44714</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09509</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12999</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11246</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12892</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.0187</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.1945</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14277</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13199</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17427</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84136</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19134</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8484700000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34124</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90396</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73477</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75786</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94913</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.64234</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.38662</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.53816</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5377799999999999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.52673</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.5302899999999999</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46167</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75587</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.36969</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.34165</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.51276</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.6070800000000001</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.60154</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.52555</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.50786</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5691900000000001</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.58496</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.58588</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.57959</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.5274800000000001</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5689299999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.5016499999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.45911</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46676</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46672</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49736</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45676</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.6351599999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54603</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.67774</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53513</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02279</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77207</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74009</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27871</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34024</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71646</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64002</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34673</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99422</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.5906</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49268</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49425</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53871</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.58917</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73236</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17557</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.6901499999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9109299999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.66383</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93257</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74375</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71301</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17487</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17606</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.4237</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23469</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61358</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20219</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28213</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07506</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.3967</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03268</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.6600199999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.63162</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.13233</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63125</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47238</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50319</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48264</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52511</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53177</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80083</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6675599999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.6486900000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50885</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66522</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.6632</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7955599999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04704</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16567</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49942</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.1919</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5459700000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15296</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55667</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57176</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49742</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47856</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50051</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53804</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.59657</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75609</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.1269</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.68398</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.54822</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45749</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58004</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44789</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46194</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46304</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.54491</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45955</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.47296</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.47766</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.49563</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.45732</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36919</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.85664</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.47879</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.43891</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.10936</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.6974400000000001</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17116</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.25936</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09616</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6877799999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5582699999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.48799</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.4656</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48396</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.0926</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36482</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8385499999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.79843</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5214500000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7527200000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7512799999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51168</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44115</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55388</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44174</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.50551</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.72763</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.5677000000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7968999999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.75258</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.4090299999999999</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52237</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28031</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28367</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21559</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.05986</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.95238</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28247</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5440199999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49091</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.74915</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54562</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.54067</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21261</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75209</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.7505700000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5745800000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49138</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98385</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7587200000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61776</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7497200000000001</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17089</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6002799999999999</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7257</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62327</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23469</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.87182</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.85733</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.87888</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.89747</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15151</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.63809</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.92999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9549299999999999</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.61744</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63551</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.7344</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.61791</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79002</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24263</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03339</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.9940399999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.00664</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51254</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.33945</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04744</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75358</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34521</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55663</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80087</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54952</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75054</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75234</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55883</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46871</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40696</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41897</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62691</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55599</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.53706</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47293</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49427</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55696</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81132</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15222</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11837</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03128</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12108</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72432</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.71907</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04211</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06048</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.6675099999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5555099999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56198</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47705</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46326</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54616</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55145</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65683</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.5408</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.0428</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65359</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54643</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49682</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49737</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49738</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48019</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57453</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55486</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55835</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49581</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51146</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49825</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5581799999999999</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6567999999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15105</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.05401</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.65807</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5797100000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86311</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6573099999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.13891</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.81152</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49213</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.50947</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49699</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5326900000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34433</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.70077</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.5760700000000001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.58258</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.71338</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.54487</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62552</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58301</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.62888</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00316</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17252</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92371</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.95985</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.00889</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.94985</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91614</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.92996</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9132400000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9155599999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.01922</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.66599</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.01616</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.11896</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10082</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.69724</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92028</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8411900000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.90807</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54129</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66538</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68786</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73627</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78634</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.19606</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07616</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01566</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32828</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01133</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11041</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91476</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75097</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.75022</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.81276</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69092</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69071</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55569</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68808</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7236699999999999</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.68408</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.74618</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6941900000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46072</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73212</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.51946</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50515</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43909</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.99271</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00619</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.89423</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01401</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.9968400000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.99703</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.15762</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06621</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.08428</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.66467</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5939500000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71687</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7040700000000001</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.0258</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69652</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.74954</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13403</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.22507</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.42537</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.19412</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.35606</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.97864</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.37327</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.73682</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.64761</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.41511</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.41692</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80716</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75446</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80159</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.55292</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7537200000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43937</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81111</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31375</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00414</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.93426</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.96048</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03386</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16253</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06165</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86448</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69351</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22195</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20847</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.2091</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15209</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86781</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09748</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10836</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10839</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13459</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10609</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.2014</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.63923</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57731</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.7306699999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6628999999999999</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18541</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.86141</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.0659</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03138</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.04824</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03622</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06932</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12837</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.0508</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.0614</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18432</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16285</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21548</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20348</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26499</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16958</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14169</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12021</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10085</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12699</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17671</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19431</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17488</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07536</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6733300000000001</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61403</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5652699999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.54796</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53021</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31384</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31103</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06792</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47902</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51988</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44085</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43233</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.4387799999999999</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43566</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43665</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42484</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43122</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42608</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84837</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.68316</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.65046</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.94074</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7517200000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15785</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30549</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44442</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43257</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45962</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54477</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25168</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85125</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.61694</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7333200000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70065</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84437</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.86582</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.21356</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77315</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5799800000000001</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.5804199999999999</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62651</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.5823200000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.73458</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60954</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.19925</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17595</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41105</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.1773</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17827</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18346</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10273</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07748</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20747</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10521</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19152</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05002</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08162</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20654</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08147</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54197</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80728</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80413</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56404</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.2129</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84914</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84963</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55913</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55457</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5625399999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539500000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5012300000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45974</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49921</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5478099999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.52032</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5204800000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5576100000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17568</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88303</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17004</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50948</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56943</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8441799999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79516</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5969800000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85294</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50082</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5436299999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17771</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70102</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55538</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17354</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54927</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5504199999999999</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5808</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79964</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5551200000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7992</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.84912</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17427</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79872</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68357</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05063</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.1749</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17583</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17713</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17506</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8242699999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73241</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6448400000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6764199999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68441</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7310599999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83488</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81809</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.61511</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80644</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75615</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13646</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.75022</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60948</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63585</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.63813</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.61713</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61451</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.70317</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67038</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.81323</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70409</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60815</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53101</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
